--- a/mario/ops/cvxlab_models/Split_sectors_MRIO_quadratic/model_settings_strict.xlsx
+++ b/mario/ops/cvxlab_models/Split_sectors_MRIO_quadratic/model_settings_strict.xlsx
@@ -934,7 +934,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>parameter: [y_weight,supply_weight,reference_floor]</t>
+          <t>parameter: [y_weight,supply_weight,reference_floor,entropy_floor]</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q65"/>
+  <dimension ref="A1:Q66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="12.81640625" customWidth="1" min="1" max="1"/>
@@ -3334,12 +3334,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>V_nonnegative_mask</t>
+          <t>Model_controls</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ones where prior zeroes</t>
+          <t>Numerical model control</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3349,37 +3349,24 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>factor, region_to, sector_to</t>
+          <t>model_control</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>V_nonnegative_mask</t>
-        </is>
-      </c>
-      <c r="H53" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>dim: cols, filters: {category: [parent, new]}</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>dim: cols</t>
-        </is>
-      </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>dim: rows</t>
+          <t>Entropy_floor</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>dim: rows, filters: {parameter: entropy_floor}</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>V_signed_mask</t>
+          <t>V_nonnegative_mask</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3399,7 +3386,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>V_signed_mask</t>
+          <t>V_nonnegative_mask</t>
         </is>
       </c>
       <c r="H54" t="n">
@@ -3424,37 +3411,35 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>V_signed_mask</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>new final consumption</t>
+          <t>ones where prior zeroes</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>endogenous</t>
+          <t>exogenous</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>region_from, region_to, sector_from, cons_categ</t>
+          <t>factor, region_to, sector_to</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Y_all</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>dim: rows, filters: {category: [parent, new]}</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>dim: rows</t>
+          <t>V_signed_mask</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>dim: cols, filters: {category: [parent, new]}</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -3462,16 +3447,16 @@
           <t>dim: cols</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>dim: cols</t>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>dim: rows</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Y0</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3481,7 +3466,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>exogenous</t>
+          <t>endogenous</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3491,7 +3476,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Y0</t>
+          <t>Y_all</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3518,12 +3503,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Zero_Y_mask</t>
+          <t>Y0</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ones where prior zeroes</t>
+          <t>new final consumption</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3538,7 +3523,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Zero_Y_all</t>
+          <t>Y0</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3565,48 +3550,45 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Z_supply</t>
+          <t>Zero_Y_mask</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>new table of intermediate consumption supply part</t>
+          <t>ones where prior zeroes</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>endogenous</t>
+          <t>exogenous</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>region_from, region_to, sector_from, sector_to</t>
+          <t>region_from, region_to, sector_from, cons_categ</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Z_supply_all</t>
-        </is>
-      </c>
-      <c r="I58" t="b">
-        <v>1</v>
+          <t>Zero_Y_all</t>
+        </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
           <t>dim: rows, filters: {category: [parent, new]}</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>dim: cols, filters: {category: [stable]}</t>
-        </is>
-      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>dim: rows</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
+        <is>
+          <t>dim: cols</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
         <is>
           <t>dim: cols</t>
         </is>
@@ -3615,7 +3597,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Z_supply0</t>
+          <t>Z_supply</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3625,7 +3607,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>exogenous</t>
+          <t>endogenous</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3635,8 +3617,11 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Z_supply0</t>
-        </is>
+          <t>Z_supply_all</t>
+        </is>
+      </c>
+      <c r="I59" t="b">
+        <v>1</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -3662,12 +3647,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Zero_supply_mask</t>
+          <t>Z_supply0</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ones where prior zeroes</t>
+          <t>new table of intermediate consumption supply part</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3682,7 +3667,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Zero_supply_all</t>
+          <t>Z_supply0</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -3709,17 +3694,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Z_use</t>
+          <t>Zero_supply_mask</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>new table of intermediate consumption use part</t>
+          <t>ones where prior zeroes</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>endogenous</t>
+          <t>exogenous</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3729,20 +3714,17 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Z_use_all</t>
-        </is>
-      </c>
-      <c r="I61" t="b">
-        <v>1</v>
+          <t>Zero_supply_all</t>
+        </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>dim: rows</t>
+          <t>dim: rows, filters: {category: [parent, new]}</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>dim: cols, filters: {category: [parent, new]}</t>
+          <t>dim: cols, filters: {category: [stable]}</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -3759,7 +3741,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Z_use0</t>
+          <t>Z_use</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3769,7 +3751,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>exogenous</t>
+          <t>endogenous</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3779,8 +3761,11 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Z_use0</t>
-        </is>
+          <t>Z_use_all</t>
+        </is>
+      </c>
+      <c r="I62" t="b">
+        <v>1</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -3806,12 +3791,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Zero_use_mask</t>
+          <t>Z_use0</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ones where prior zeroes</t>
+          <t>new table of intermediate consumption use part</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3826,7 +3811,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Zero_use_all</t>
+          <t>Z_use0</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -3853,7 +3838,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Positive_Y_mask</t>
+          <t>Zero_use_mask</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3868,20 +3853,22 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>region_from, region_to, sector_from, cons_categ</t>
+          <t>region_from, region_to, sector_from, sector_to</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Positive_Y_mask</t>
-        </is>
-      </c>
-      <c r="H64" t="n">
-        <v>0</v>
+          <t>Zero_use_all</t>
+        </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>dim: rows, filters: {category: [parent, new]}</t>
+          <t>dim: rows</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>dim: cols, filters: {category: [parent, new]}</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -3890,11 +3877,6 @@
         </is>
       </c>
       <c r="M64" t="inlineStr">
-        <is>
-          <t>dim: intra</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr">
         <is>
           <t>dim: cols</t>
         </is>
@@ -3903,7 +3885,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Negative_Y_mask</t>
+          <t>Positive_Y_mask</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3923,7 +3905,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Negative_Y_mask</t>
+          <t>Positive_Y_mask</t>
         </is>
       </c>
       <c r="H65" t="n">
@@ -3945,6 +3927,56 @@
         </is>
       </c>
       <c r="N65" t="inlineStr">
+        <is>
+          <t>dim: cols</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Negative_Y_mask</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>ones where prior zeroes</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>exogenous</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>region_from, region_to, sector_from, cons_categ</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Negative_Y_mask</t>
+        </is>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>dim: rows, filters: {category: [parent, new]}</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>dim: rows</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>dim: intra</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
         <is>
           <t>dim: cols</t>
         </is>
